--- a/public/downloads/templates/weekly-campaign-monitoring-sheet.xlsx
+++ b/public/downloads/templates/weekly-campaign-monitoring-sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly Monitoring" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Monitoring" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -109,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,13 +121,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -546,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,6 +592,13 @@
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Campaigns spending above this share of daily budget get flagged Near Cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Project Amazon PH Academy — Download Center</t>
         </is>
       </c>
     </row>
@@ -598,6 +607,14 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -695,7 +712,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -703,10 +720,10 @@
           <t>SP — Auto</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="16" t="n">
         <v>24.1</v>
       </c>
       <c r="E5" s="11">
@@ -723,7 +740,7 @@
         <f>IFERROR(G5/F5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="16" t="n">
         <v>620</v>
       </c>
       <c r="J5" s="11">
@@ -736,7 +753,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -744,10 +761,10 @@
           <t>SP — Exact Match Winners</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="16" t="n">
         <v>39.8</v>
       </c>
       <c r="E6" s="11">
@@ -764,7 +781,7 @@
         <f>IFERROR(G6/F6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="16" t="n">
         <v>2340</v>
       </c>
       <c r="J6" s="11">
@@ -777,7 +794,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -785,10 +802,10 @@
           <t>SB — Brand Defense</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="11">
@@ -805,7 +822,7 @@
         <f>IFERROR(G7/F7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="I7" s="16" t="n">
         <v>410</v>
       </c>
       <c r="J7" s="11">
@@ -818,7 +835,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -826,10 +843,10 @@
           <t>SD — Retargeting</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="16" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E8" s="11">
@@ -846,7 +863,7 @@
         <f>IFERROR(G8/F8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="16" t="n">
         <v>96</v>
       </c>
       <c r="J8" s="11">
@@ -859,7 +876,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -867,10 +884,10 @@
           <t>SP — Broad Match Discovery</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="16" t="n">
         <v>19.9</v>
       </c>
       <c r="E9" s="11">
@@ -887,7 +904,7 @@
         <f>IFERROR(G9/F9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="16" t="n">
         <v>260</v>
       </c>
       <c r="J9" s="11">
@@ -916,5 +933,13 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;9 Project Amazon PH Academy — Download Center</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>